--- a/bpc_upload_template/BPC1_WC_Upload_Template.xlsx
+++ b/bpc_upload_template/BPC1_WC_Upload_Template.xlsx
@@ -507,7 +507,7 @@
     <row r="1" ht="35" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BPC2 Wins &amp; Challenges Upload Template</t>
+          <t>BPC1 Wins &amp; Challenges Upload Template</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
@@ -1017,7 +1017,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
@@ -1185,7 +1185,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>

--- a/bpc_upload_template/BPC1_WC_Upload_Template.xlsx
+++ b/bpc_upload_template/BPC1_WC_Upload_Template.xlsx
@@ -849,7 +849,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
@@ -1017,7 +1016,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
@@ -1185,7 +1183,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
